--- a/templates/PMO_산출물_표준양식_v1.2.xlsx
+++ b/templates/PMO_산출물_표준양식_v1.2.xlsx
@@ -670,7 +670,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>02_회의록대장            결정사항 / 미결사항 — 노사협의 유형 포함</t>
+          <t>02_회의록대장            결정사항 / 미결사항 — 현업협의·의사결정 유형 포함</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>DS-014 근무유형·근태규칙 표준 정의서   현행 47종 → 표준 14종 매핑 전건</t>
+          <t>DS-014 근무유형·근태규칙 표준 정의서   47→14 매핑 + 특이근태 예외 23종</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>계획진척률 과소 산정 · SPI 왜곡(실제보다 나쁘게 보임)</t>
+          <t>계획진척률 과소 산정 · 지연일수 과대 집계(실제보다 나쁘게 보임)</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="T20" s="9" t="inlineStr">
         <is>
-          <t>47종→14종 노사 합의 3회 이월(ISS-014)</t>
+          <t>특이근태 예외 23종 중 14종 처리 방침 미확정(ISS-014)</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       <c r="S28" s="9" t="inlineStr"/>
       <c r="T28" s="9" t="inlineStr">
         <is>
-          <t>노사협의회 합의 조건(MT-2026-031 D-02)</t>
+          <t>현업 합의 조건(MT-2026-031 D-02)</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -3630,21 +3630,21 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr"/>
       <c r="K29" s="9" t="n">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>18.6</v>
+        <v>14</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="O29" s="9" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -3706,21 +3706,21 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>42.9</v>
+        <v>33</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>5.1.4</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
@@ -3757,50 +3757,54 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>점포·조직 권한 및 결재선 모듈 개발</t>
+          <t>공통 프레임워크·개발표준 적용</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>벼리</t>
+          <t>초롱</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K31" s="9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N31" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O31" s="9" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="P31" s="9" t="inlineStr">
@@ -3811,28 +3815,20 @@
       <c r="Q31" s="9" t="inlineStr"/>
       <c r="R31" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="S31" s="9" t="inlineStr">
-        <is>
-          <t>RC-05</t>
-        </is>
-      </c>
-      <c r="T31" s="9" t="inlineStr">
-        <is>
-          <t>점포유형별 결재선 매트릭스 미확정(AI-072)</t>
-        </is>
-      </c>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="S31" s="9" t="inlineStr"/>
+      <c r="T31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
@@ -3841,66 +3837,78 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>근태 도메인 개발</t>
+          <t>인증·SSO 모듈 개발</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>벼리</t>
+          <t>초롱</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K32" s="9" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M32" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="P32" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q32" s="9" t="inlineStr"/>
       <c r="R32" s="9" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="S32" s="9" t="inlineStr"/>
-      <c r="T32" s="9" t="inlineStr"/>
+      <c r="T32" s="9" t="inlineStr">
+        <is>
+          <t>CR-2026-003 OAuth2.0 반영</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.3</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
@@ -3913,7 +3921,7 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>수당 산정 모듈 개발(연장·야간·휴일)</t>
+          <t>공통 코드·마스터 관리 개발</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3928,59 +3936,63 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr"/>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="K33" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33" s="9" t="inlineStr">
         <is>
-          <t>4.2.3;4.5.2</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr"/>
       <c r="R33" s="9" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="S33" s="9" t="inlineStr"/>
-      <c r="T33" s="9" t="inlineStr">
-        <is>
-          <t>CR-2026-007 영향 +12MD</t>
-        </is>
-      </c>
+      <c r="T33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
@@ -3989,70 +4001,82 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>근태단말 연계 개발(1,240대)</t>
+          <t>점포·조직 권한 매트릭스 적용</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>바름</t>
+          <t>벼리</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr"/>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="J34" s="9" t="inlineStr"/>
       <c r="K34" s="9" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34" s="9" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="P34" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q34" s="9" t="inlineStr"/>
       <c r="R34" s="9" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="S34" s="9" t="inlineStr"/>
-      <c r="T34" s="9" t="inlineStr"/>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>RC-05</t>
+        </is>
+      </c>
+      <c r="T34" s="9" t="inlineStr">
+        <is>
+          <t>권한 매트릭스 미확정(AI-072)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.1.5</t>
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -4061,7 +4085,7 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>AI 스케줄 엔진 개발</t>
+          <t>결재선 엔진 개발</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -4076,40 +4100,40 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr"/>
       <c r="K35" s="9" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="P35" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr"/>
@@ -4119,16 +4143,12 @@
         </is>
       </c>
       <c r="S35" s="9" t="inlineStr"/>
-      <c r="T35" s="9" t="inlineStr">
-        <is>
-          <t>AI 자동편성 과업</t>
-        </is>
-      </c>
+      <c r="T35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.1.6</t>
         </is>
       </c>
       <c r="B36" s="9" t="n">
@@ -4141,78 +4161,66 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>배정 최적화 엔진 개발(CP-SAT)</t>
+          <t>공통 화면 컴포넌트 개발</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>벼리</t>
+          <t>여울</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>기획</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr"/>
       <c r="K36" s="9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O36" s="9" t="inlineStr">
         <is>
-          <t>4.6.3;4.3.2</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="P36" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q36" s="9" t="inlineStr"/>
       <c r="R36" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
-        </is>
-      </c>
-      <c r="S36" s="9" t="inlineStr">
-        <is>
-          <t>RC-03</t>
-        </is>
-      </c>
-      <c r="T36" s="9" t="inlineStr">
-        <is>
-          <t>선행 4.3.2 미완(70%) · 정의역 미확정</t>
-        </is>
-      </c>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S36" s="9" t="inlineStr"/>
+      <c r="T36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.1.7</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
@@ -4225,33 +4233,33 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>소요 확정·가용인력 산정 배치 개발</t>
+          <t>공통 모듈 단위테스트</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>새벽</t>
+          <t>모아</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr"/>
       <c r="J37" s="9" t="inlineStr"/>
       <c r="K37" s="9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0</v>
@@ -4264,12 +4272,12 @@
       </c>
       <c r="O37" s="9" t="inlineStr">
         <is>
-          <t>4.6.2</t>
+          <t>5.1.5</t>
         </is>
       </c>
       <c r="P37" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr"/>
@@ -4284,11 +4292,11 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -4297,33 +4305,33 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>점포장 조정·재최적화 개발</t>
+          <t>근태 도메인 개발</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>초롱</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>도메인</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr"/>
       <c r="K38" s="9" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0</v>
@@ -4332,16 +4340,16 @@
         <v>0</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="9" t="inlineStr">
         <is>
-          <t>5.4.1;4.6.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="P38" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="Q38" s="9" t="inlineStr"/>
@@ -4356,46 +4364,46 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>테스트</t>
+          <t>구현</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>통합·급여 병행운영·파일럿 점포 테스트</t>
+          <t>근태 규칙 엔진 – 근로시간 판정</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>모아</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>도메인</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr"/>
       <c r="J39" s="9" t="inlineStr"/>
       <c r="K39" s="9" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>0</v>
@@ -4404,11 +4412,11 @@
         <v>0</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O39" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.3.2;3.2.2</t>
         </is>
       </c>
       <c r="P39" s="9" t="inlineStr">
@@ -4428,46 +4436,46 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>테스트</t>
+          <t>구현</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>급여 병행운영 검증(2개월분)</t>
+          <t>근태 규칙 엔진 – 특이근태 예외 처리</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>모아</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>도메인</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>0</v>
@@ -4480,7 +4488,7 @@
       </c>
       <c r="O40" s="9" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2.1;4.3.2</t>
         </is>
       </c>
       <c r="P40" s="9" t="inlineStr">
@@ -4488,11 +4496,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="Q40" s="9" t="inlineStr">
-        <is>
-          <t>DS-021</t>
-        </is>
-      </c>
+      <c r="Q40" s="9" t="inlineStr"/>
       <c r="R40" s="9" t="inlineStr">
         <is>
           <t>미착수</t>
@@ -4501,53 +4505,53 @@
       <c r="S40" s="9" t="inlineStr"/>
       <c r="T40" s="9" t="inlineStr">
         <is>
-          <t>급여 마감 주기 종속 · 압축 불가</t>
+          <t>예외 14종 확정 대기</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.2.3</t>
         </is>
       </c>
       <c r="B41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>테스트</t>
+          <t>구현</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>AI 엔진 검증(SLA 8종)</t>
+          <t>수당 산정 – 연장·야간</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>모아</t>
+          <t>초롱</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr"/>
       <c r="K41" s="9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>0</v>
@@ -4560,74 +4564,66 @@
       </c>
       <c r="O41" s="9" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="P41" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q41" s="9" t="inlineStr">
-        <is>
-          <t>DS-015</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q41" s="9" t="inlineStr"/>
       <c r="R41" s="9" t="inlineStr">
         <is>
           <t>미착수</t>
         </is>
       </c>
       <c r="S41" s="9" t="inlineStr"/>
-      <c r="T41" s="9" t="inlineStr">
-        <is>
-          <t>법정제약 0건·충족률·형평성 지니·최적화시간</t>
-        </is>
-      </c>
+      <c r="T41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.2.4</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>이행</t>
+          <t>구현</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>이행 및 전점 확산(71개점) · 오픈</t>
+          <t>수당 산정 – 휴일·중복가산</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>나루</t>
+          <t>초롱</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr"/>
       <c r="K42" s="9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>0</v>
@@ -4640,12 +4636,12 @@
       </c>
       <c r="O42" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.2.3</t>
         </is>
       </c>
       <c r="P42" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q42" s="9" t="inlineStr"/>
@@ -4655,55 +4651,51 @@
         </is>
       </c>
       <c r="S42" s="9" t="inlineStr"/>
-      <c r="T42" s="9" t="inlineStr">
-        <is>
-          <t>변경 동결 12-14 이전 오픈 필수</t>
-        </is>
-      </c>
+      <c r="T42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.2.5</t>
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>안정화</t>
+          <t>구현</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>안정화 및 종료</t>
+          <t>출퇴근 기록·사후 보정 처리</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>나루</t>
+          <t>바름</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0</v>
@@ -4716,12 +4708,12 @@
       </c>
       <c r="O43" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="P43" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q43" s="9" t="inlineStr"/>
@@ -4732,6 +4724,2722 @@
       </c>
       <c r="S43" s="9" t="inlineStr"/>
       <c r="T43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>근태 신청·승인 워크플로 개발</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>여울</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t>5.1.5</t>
+        </is>
+      </c>
+      <c r="P44" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S44" s="9" t="inlineStr"/>
+      <c r="T44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>5.2.7</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>근태 도메인 단위테스트</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr"/>
+      <c r="K45" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="9" t="inlineStr">
+        <is>
+          <t>5.2.4</t>
+        </is>
+      </c>
+      <c r="P45" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q45" s="9" t="inlineStr"/>
+      <c r="R45" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S45" s="9" t="inlineStr"/>
+      <c r="T45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>근태단말 연계 개발(1,240대)</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>바름</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr"/>
+      <c r="K46" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t>4.4.1</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q46" s="9" t="inlineStr"/>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S46" s="9" t="inlineStr"/>
+      <c r="T46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>5.3.1</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>단말 통신 프로토콜 어댑터</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>바름</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr"/>
+      <c r="K47" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="9" t="inlineStr">
+        <is>
+          <t>4.4.1</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="inlineStr"/>
+      <c r="R47" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S47" s="9" t="inlineStr"/>
+      <c r="T47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>5.3.2</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>생체인증 데이터 연계</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>바름</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr"/>
+      <c r="K48" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>5.3.1</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q48" s="9" t="inlineStr"/>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S48" s="9" t="inlineStr"/>
+      <c r="T48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>5.3.3</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>확정 스케줄 하향 전송 배치</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>바름</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr"/>
+      <c r="K49" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>5.3.1;5.4.6</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q49" s="9" t="inlineStr"/>
+      <c r="R49" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S49" s="9" t="inlineStr"/>
+      <c r="T49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>5.3.4</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>단말 상태 모니터링·장애 처리</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>초롱</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr"/>
+      <c r="K50" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>5.3.2</t>
+        </is>
+      </c>
+      <c r="P50" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q50" s="9" t="inlineStr"/>
+      <c r="R50" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S50" s="9" t="inlineStr"/>
+      <c r="T50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>5.3.5</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>단말 연계 단위테스트</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr"/>
+      <c r="J51" s="9" t="inlineStr"/>
+      <c r="K51" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>5.3.3</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q51" s="9" t="inlineStr"/>
+      <c r="R51" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S51" s="9" t="inlineStr"/>
+      <c r="T51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>AI 스케줄 엔진 개발</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>벼리</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr"/>
+      <c r="K52" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M52" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="O52" s="9" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="P52" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q52" s="9" t="inlineStr"/>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="S52" s="9" t="inlineStr"/>
+      <c r="T52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>5.4.1</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>배정 최적화 – 제약 모델 구현</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>벼리</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr"/>
+      <c r="K53" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N53" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="O53" s="9" t="inlineStr">
+        <is>
+          <t>4.6.3;4.3.2</t>
+        </is>
+      </c>
+      <c r="P53" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q53" s="9" t="inlineStr"/>
+      <c r="R53" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="S53" s="9" t="inlineStr">
+        <is>
+          <t>RC-03</t>
+        </is>
+      </c>
+      <c r="T53" s="9" t="inlineStr">
+        <is>
+          <t>선행 4.3.2 미완 · 예외 5종 미확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>5.4.2</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>배정 최적화 – 목적함수·형평성 구현</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr"/>
+      <c r="K54" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t>5.4.1</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q54" s="9" t="inlineStr"/>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S54" s="9" t="inlineStr"/>
+      <c r="T54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>5.4.3</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>소요 확정·가용인력 산정 모듈</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr"/>
+      <c r="J55" s="9" t="inlineStr"/>
+      <c r="K55" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O55" s="9" t="inlineStr">
+        <is>
+          <t>4.6.1</t>
+        </is>
+      </c>
+      <c r="P55" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q55" s="9" t="inlineStr"/>
+      <c r="R55" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S55" s="9" t="inlineStr"/>
+      <c r="T55" s="9" t="inlineStr">
+        <is>
+          <t>기준정보 27개점 미확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>5.4.4</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>솔버 튜닝·성능 최적화</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr"/>
+      <c r="K56" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="9" t="inlineStr">
+        <is>
+          <t>5.4.2</t>
+        </is>
+      </c>
+      <c r="P56" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q56" s="9" t="inlineStr"/>
+      <c r="R56" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S56" s="9" t="inlineStr"/>
+      <c r="T56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>5.4.5</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>배정 근거(XAI) 생성 모듈</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr"/>
+      <c r="K57" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="9" t="inlineStr">
+        <is>
+          <t>5.4.2;4.6.4</t>
+        </is>
+      </c>
+      <c r="P57" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q57" s="9" t="inlineStr"/>
+      <c r="R57" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S57" s="9" t="inlineStr"/>
+      <c r="T57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>5.4.6</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>점포장 조정·부분 재최적화 개발</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>초롱</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr"/>
+      <c r="J58" s="9" t="inlineStr"/>
+      <c r="K58" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t>5.4.4</t>
+        </is>
+      </c>
+      <c r="P58" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q58" s="9" t="inlineStr"/>
+      <c r="R58" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S58" s="9" t="inlineStr"/>
+      <c r="T58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>5.4.7</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>편성 배치 스케줄러 개발</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>벼리</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr"/>
+      <c r="K59" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
+          <t>5.4.6</t>
+        </is>
+      </c>
+      <c r="P59" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q59" s="9" t="inlineStr"/>
+      <c r="R59" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S59" s="9" t="inlineStr"/>
+      <c r="T59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>5.4.8</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>AI 엔진 단위테스트</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr"/>
+      <c r="K60" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>5.4.7</t>
+        </is>
+      </c>
+      <c r="P60" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q60" s="9" t="inlineStr"/>
+      <c r="R60" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S60" s="9" t="inlineStr"/>
+      <c r="T60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>점포 관리자 포털 개발</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>여울</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr"/>
+      <c r="K61" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="L61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="P61" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q61" s="9" t="inlineStr"/>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S61" s="9" t="inlineStr"/>
+      <c r="T61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>5.5.1</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>점포 관리자 대시보드 개발</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>여울</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr"/>
+      <c r="K62" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="9" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="P62" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q62" s="9" t="inlineStr"/>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S62" s="9" t="inlineStr"/>
+      <c r="T62" s="9" t="inlineStr">
+        <is>
+          <t>CR-2026-009 심의 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>5.5.2</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>편성 검토·조정 화면 개발</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>여울</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>5.4.5</t>
+        </is>
+      </c>
+      <c r="P63" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q63" s="9" t="inlineStr"/>
+      <c r="R63" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S63" s="9" t="inlineStr"/>
+      <c r="T63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>5.5.3</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>근태 현황·통계 조회 개발</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>초롱</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr"/>
+      <c r="K64" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="9" t="inlineStr">
+        <is>
+          <t>5.2.5</t>
+        </is>
+      </c>
+      <c r="P64" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q64" s="9" t="inlineStr"/>
+      <c r="R64" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S64" s="9" t="inlineStr"/>
+      <c r="T64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>5.5.4</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>관리자 포털 단위테스트</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t>5.5.2</t>
+        </is>
+      </c>
+      <c r="P65" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q65" s="9" t="inlineStr"/>
+      <c r="R65" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S65" s="9" t="inlineStr"/>
+      <c r="T65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>모바일 앱 개발</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>여울</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr"/>
+      <c r="K66" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="L66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="9" t="inlineStr">
+        <is>
+          <t>4.2.3</t>
+        </is>
+      </c>
+      <c r="P66" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q66" s="9" t="inlineStr"/>
+      <c r="R66" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S66" s="9" t="inlineStr"/>
+      <c r="T66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>5.6.1</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>모바일 출퇴근 체크 개발</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>바름</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr"/>
+      <c r="K67" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="9" t="inlineStr">
+        <is>
+          <t>4.2.3</t>
+        </is>
+      </c>
+      <c r="P67" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q67" s="9" t="inlineStr"/>
+      <c r="R67" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S67" s="9" t="inlineStr"/>
+      <c r="T67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>5.6.2</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>휴게시간 자동분할·근로자 확인 개발</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>바름</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr"/>
+      <c r="K68" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="9" t="inlineStr">
+        <is>
+          <t>5.6.1</t>
+        </is>
+      </c>
+      <c r="P68" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q68" s="9" t="inlineStr"/>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr"/>
+      <c r="T68" s="9" t="inlineStr">
+        <is>
+          <t>CR-2026-007 영향 +12MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>5.6.3</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>근태 신청·희망근무 등록 개발</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>초롱</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr"/>
+      <c r="K69" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="P69" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q69" s="9" t="inlineStr"/>
+      <c r="R69" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S69" s="9" t="inlineStr"/>
+      <c r="T69" s="9" t="inlineStr">
+        <is>
+          <t>희망 신청 채널 — 시뮬레이션 선행조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>5.6.4</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>스케줄 조회·배정 근거 표시 개발</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>초롱</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr"/>
+      <c r="K70" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t>5.4.5</t>
+        </is>
+      </c>
+      <c r="P70" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q70" s="9" t="inlineStr"/>
+      <c r="R70" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S70" s="9" t="inlineStr"/>
+      <c r="T70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>5.6.5</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>모바일 단위테스트</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr"/>
+      <c r="K71" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t>5.6.4</t>
+        </is>
+      </c>
+      <c r="P71" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q71" s="9" t="inlineStr"/>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S71" s="9" t="inlineStr"/>
+      <c r="T71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>급여 연계 개발</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>너울</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr"/>
+      <c r="J72" s="9" t="inlineStr"/>
+      <c r="K72" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t>4.5.2</t>
+        </is>
+      </c>
+      <c r="P72" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q72" s="9" t="inlineStr"/>
+      <c r="R72" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S72" s="9" t="inlineStr"/>
+      <c r="T72" s="9" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>5.7.1</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>급여 I/F 송수신 모듈 개발</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>너울</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t>4.5.2</t>
+        </is>
+      </c>
+      <c r="P73" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q73" s="9" t="inlineStr"/>
+      <c r="R73" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S73" s="9" t="inlineStr"/>
+      <c r="T73" s="9" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>5.7.2</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>근태 데이터 이관 프로그램 개발</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>너울</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr"/>
+      <c r="J74" s="9" t="inlineStr"/>
+      <c r="K74" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t>5.7.1</t>
+        </is>
+      </c>
+      <c r="P74" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q74" s="9" t="inlineStr"/>
+      <c r="R74" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S74" s="9" t="inlineStr"/>
+      <c r="T74" s="9" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>5.7.3</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>정합성 대사 배치 개발</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>너울</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr"/>
+      <c r="J75" s="9" t="inlineStr"/>
+      <c r="K75" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t>5.7.2</t>
+        </is>
+      </c>
+      <c r="P75" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q75" s="9" t="inlineStr"/>
+      <c r="R75" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S75" s="9" t="inlineStr"/>
+      <c r="T75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>통합·급여 병행운영·파일럿 점포 테스트</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr"/>
+      <c r="J76" s="9" t="inlineStr"/>
+      <c r="K76" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="L76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P76" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q76" s="9" t="inlineStr"/>
+      <c r="R76" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S76" s="9" t="inlineStr"/>
+      <c r="T76" s="9" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>급여 병행운영 검증(2개월분)</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr"/>
+      <c r="K77" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="P77" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q77" s="9" t="inlineStr">
+        <is>
+          <t>DS-021</t>
+        </is>
+      </c>
+      <c r="R77" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S77" s="9" t="inlineStr"/>
+      <c r="T77" s="9" t="inlineStr">
+        <is>
+          <t>급여 마감 주기 종속 · 압축 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>AI 엔진 검증(SLA 8종)</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>모아</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr"/>
+      <c r="K78" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="L78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="P78" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q78" s="9" t="inlineStr">
+        <is>
+          <t>DS-015</t>
+        </is>
+      </c>
+      <c r="R78" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S78" s="9" t="inlineStr"/>
+      <c r="T78" s="9" t="inlineStr">
+        <is>
+          <t>법정제약 0건·충족률·형평성 지니·최적화시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>이행</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>이행 및 전점 확산(71개점) · 오픈</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>나루</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr"/>
+      <c r="K79" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="L79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P79" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q79" s="9" t="inlineStr"/>
+      <c r="R79" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S79" s="9" t="inlineStr"/>
+      <c r="T79" s="9" t="inlineStr">
+        <is>
+          <t>변경 동결 12-14 이전 오픈 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>안정화</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>안정화 및 종료</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>나루</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P80" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q80" s="9" t="inlineStr"/>
+      <c r="R80" s="9" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="S80" s="9" t="inlineStr"/>
+      <c r="T80" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4871,7 +7579,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>정기주간/설계리뷰/이슈해결/고객협의/운영위/대외협의/노사협의</t>
+          <t>정기주간/설계리뷰/이슈해결/현업협의/운영위/대외협의/의사결정</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr"/>
@@ -5066,7 +7774,7 @@
       </c>
       <c r="O5" s="9" t="inlineStr">
         <is>
-          <t>탄력근로제 단위기간 3개월/6개월 (결정필요일 2026-09-18 / 결정권자: 인사팀장 + 노사협의회)</t>
+          <t>탄력근로제 단위기간 3개월/6개월 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀장)</t>
         </is>
       </c>
       <c r="P5" s="9" t="inlineStr">
@@ -5088,12 +7796,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>근무유형 표준 통합안 1차 노사협의</t>
+          <t>특이근태 예외 처리 방침 1차 협의</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>노사협의</t>
+          <t>의사결정</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -5103,7 +7811,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>노측 4인, 사측 인사팀 3인, PM, 두루</t>
+          <t>고객 인사팀 3인, 점포운영팀 2인, PM, 두루</t>
         </is>
       </c>
       <c r="G6" s="9" t="n">
@@ -5135,12 +7843,12 @@
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>D-01 근무 도메인 모델 확정 · D-02 AI 편성 근거 3종 제공 의무화 · D-03 형평성 가중치 0.12→0.30 상향(최상위)</t>
+          <t>D-01 근무 도메인 모델 확정 · D-02 편성 근거 3종 제공 의무화 · D-03 형평성 가중치 0.12→0.30 상향(최상위) · 예외 9종 처리 방침 확정</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>교대 근무유형 표준 14종 통합안 합의 (결정필요일 2026-09-18 / 결정권자: 노사협의회)</t>
+          <t>특이근태 예외 23종 중 미결 14종 처리 방침 확정 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
         </is>
       </c>
       <c r="P6" s="9" t="inlineStr">
@@ -5284,7 +7992,7 @@
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>근무유형 표준 합의 2회차 이월 (결정필요일 2026-10-01 / 결정권자: 노사협의회)</t>
+          <t>특이근태 예외 처리 방침 2회차 이월 (결정필요일 2026-10-01 / 결정권자: 고객 인사팀)</t>
         </is>
       </c>
       <c r="P8" s="9" t="inlineStr">
@@ -5380,12 +8088,12 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>근무유형 표준 3차 노사협의</t>
+          <t>특이근태 예외 처리 방침 3차 협의</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>노사협의</t>
+          <t>의사결정</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -5395,7 +8103,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>노측 4인, 사측 인사팀 3인, PM</t>
+          <t>고객 인사팀 3인, 급여팀 1인, PM</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
@@ -5427,12 +8135,12 @@
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>이견 없는 9종 우선 확정 검토 · Mock 제약셋 기반 병행개발 착수</t>
+          <t>확정 9종 기준 제약셋 우선 구현 · 미결 14종은 후처리 필터로 임시 우회 결정</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>쟁점 5종(WT-04/07/09/13/14) 합의 3회차 이월 (결정필요일 2026-09-18 / 결정권자: 노사협의회)</t>
+          <t>하드 제약 충돌 5종(E-04/07/09/12/19) 방침 3회차 이월 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -5497,7 +8205,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>개발 2명 증원 품의 · 노사협의회 긴급 상정 · 기준 수립 워크숍 개최 합의</t>
+          <t>개발 2명 증원 품의 · 현업 의사결정 단일창구(인사팀 TF) 설치 · 기준 수립 워크숍 개최 합의</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
@@ -5576,7 +8284,7 @@
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>형평성 누적 대상 기간 3/6/12개월 (결정필요일 2026-10-16 / 결정권자: 노사협의회)</t>
+          <t>형평성 누적 대상 기간 3/6/12개월 (결정필요일 2026-10-16 / 결정권자: 고객 인사팀)</t>
         </is>
       </c>
       <c r="P12" s="9" t="inlineStr">
@@ -6073,7 +8781,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>근무유형 47종 → 표준 14종 매핑안 작성 및 노사협의회 상정</t>
+          <t>특이근태 예외 케이스 전수 도출 및 처리 방침(안) 작성</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -6131,7 +8839,7 @@
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>완료(2일 초과). 노사협의회 상정 대기</t>
+          <t>23종 도출 완료(2일 초과). 9종 확정 / 14종 인사팀 회신 대기</t>
         </is>
       </c>
     </row>
@@ -6148,7 +8856,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>합의 9종 기준 제약셋 정의 및 최적화 엔진 병행개발 착수</t>
+          <t>확정 9종 기준 제약셋 정의 및 최적화 엔진 병행개발 착수</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -6831,12 +9539,12 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>근무유형 표준 미확정으로 후속 설계·개발 착수 불가</t>
+          <t>특이근태 예외 처리 방침 미확정으로 제약식 확정 불가</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>근무유형 47종→표준 14종 통합안 노사 합의가 3회 이월. 쟁점 5종 미확정으로 AI 배정 최적화의 결정 변수 정의역이 닫히지 않음</t>
+          <t>자동편성 로직 수립 중 표준 14종으로 판정 불가한 특이근태 23종 도출. 9종만 확정되고 14종은 현업 회신 대기. 이 중 5종은 하드 제약과 직접 충돌해 제약식을 확정할 수 없음</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -6872,7 +9580,7 @@
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>10-12 노사협의회 긴급 상정. 결정 SLA 3영업일 요청. 이견 없는 9종 우선 확정 추진</t>
+          <t>인사팀 TF 단일창구 설치(10-12). 결정 SLA 3영업일 요청. 확정 9종 기준 선구현, 미결 14종은 후처리 필터 우회</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
@@ -6888,7 +9596,7 @@
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>노사협의회</t>
+          <t>고객 인사팀</t>
         </is>
       </c>
     </row>
@@ -8513,14 +11221,13 @@
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -8573,40 +11280,35 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>영향비용(천원)</t>
+          <t>영향일정(일)</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>영향일정(일)</t>
+          <t>심의일</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>심의일</t>
+          <t>승인상태</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>승인상태</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
           <t>승인일</t>
         </is>
       </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>연관WBS_ID</t>
+        </is>
+      </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>연관WBS_ID</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
           <t>재기준선반영</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>반영일</t>
         </is>
@@ -8652,35 +11354,30 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>숫자</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
+          <t>심의대기/승인/조건부승인/반려 · 필수</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>심의대기/승인/조건부승인/반려 · 필수</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>세미콜론(;) · 필수</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>세미콜론(;) · 필수</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
           <t>Y/N · N이면 계획-실적 왜곡 발생</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
@@ -8726,37 +11423,34 @@
         <v>12</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>8400</v>
-      </c>
-      <c r="J4" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>4.2.3;5.2.3</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t>4.2.3;5.2.3</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P4" s="9" t="inlineStr"/>
+      <c r="O4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -8798,37 +11492,34 @@
         <v>6</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="J5" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>4.2.2;5.4.3</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>4.2.2;5.4.3</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -8874,29 +11565,26 @@
         <v>9</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>6300</v>
-      </c>
-      <c r="J6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>심의대기</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>5.4.3</t>
+        </is>
+      </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>5.4.3</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P6" s="9" t="inlineStr"/>
+      <c r="O6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -8938,37 +11626,34 @@
         <v>8</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>5600</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
@@ -9002,7 +11687,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>노사협의회 결정사항 D-02(편성 근거 제공) 실효성 확보</t>
+          <t>현업 협의 결정사항 D-02(편성 근거 제공) 실효성 확보</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -9108,7 +11793,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9302,12 +11987,12 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>회의록·노사협의 미결사항, 액션아이템</t>
+          <t>회의록 미결사항, 액션아이템</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>운영위·노사협의회 긴급 상정, 결정 SLA(3영업일), 잠정안 기준 병행 착수</t>
+          <t>운영위·현업 의사결정 회의체 긴급 상정, 결정 SLA(3영업일), 잠정안 기준 병행 착수</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -9527,7 +12212,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>대외기관·타사·고객·노조 측 산출물이나 회신 지연으로 진행 불가</t>
+          <t>대외기관·타사·고객 현업 측 산출물이나 회신 지연으로 진행 불가</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -9537,7 +12222,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>이슈대장, 대외·노사협의 회의록</t>
+          <t>이슈대장, 대외·현업협의 회의록</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -9883,7 +12568,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>운영위·노사협의회 긴급 상정 · 결정 SLA 3일</t>
+          <t>운영위·현업 회의체 긴급 상정 · 결정 SLA 3일</t>
         </is>
       </c>
     </row>

--- a/templates/PMO_산출물_표준양식_v1.2.xlsx
+++ b/templates/PMO_산출물_표준양식_v1.2.xlsx
@@ -1586,13 +1586,13 @@
         <v>54</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>48.6</v>
+        <v>54.3</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>48.6</v>
+        <v>54.3</v>
       </c>
       <c r="O4" s="9" t="inlineStr"/>
       <c r="P4" s="9" t="inlineStr">
@@ -2236,7 +2236,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>100</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>86.7</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>100</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>71</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>100</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>78.59999999999999</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>100</v>
+        <v>70.7</v>
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>65</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>72</v>
+        <v>62.7</v>
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>61.3</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>100</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>40</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>55</v>
+        <v>69.2</v>
       </c>
       <c r="O27" s="9" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>15</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>33</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>20</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O38" s="9" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O39" s="9" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>8</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>22</v>
+        <v>28.3</v>
       </c>
       <c r="O52" s="9" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O54" s="9" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7638,170 +7638,166 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-029</t>
+          <t>MT-2026-021</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>편성 기준정보 수집 현황 점검</t>
+          <t>착수보고 및 수행계획 확정</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>고객협의</t>
+          <t>운영위</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>새벽</t>
+          <t>미르</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>새벽, 너울, 고객 점포운영팀 3인</t>
+          <t>운영위원 6인, PM, PMO, 전체 PL</t>
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>4.6.1;4.6.2</t>
+          <t>2;3</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>DS-016</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>AI-069;AI-088</t>
-        </is>
-      </c>
+          <t>DS-001;DS-002</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr"/>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t>수집 템플릿 확정 · 대표 패턴만 입력 후 배수 규칙 자동 확장 합의</t>
+          <t>수행계획서·WBS 기준선 승인 · 주간 진척회의 매주 수요일 확정</t>
         </is>
       </c>
       <c r="O4" s="9" t="inlineStr">
         <is>
-          <t>미회신 27개점 필요인원 기준 확정 (결정필요일 2026-09-29 / 결정권자: 고객 점포운영팀)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-029.md</t>
+          <t>./minutes/MT-2026-021.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-030</t>
+          <t>MT-2026-022</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>근로시간 준수 요건 확인 고객협의</t>
+          <t>제4주차 정기 진척회의</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>고객협의</t>
+          <t>정기주간</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>도담</t>
+          <t>나루</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>도담, 나루, 고객 인사팀 2인</t>
+          <t>전체 PL 5인, PMO</t>
         </is>
       </c>
       <c r="G5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>DS-006</t>
+          <t>DS-003</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>AI-065</t>
+          <t>AI-041</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>휴게시간 자동 분할 기록 원칙 확정</t>
+          <t>AS-IS 실태조사 대상 점포 71개점 확정</t>
         </is>
       </c>
       <c r="O5" s="9" t="inlineStr">
         <is>
-          <t>탄력근로제 단위기간 3개월/6개월 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀장)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-030.md</t>
+          <t>./minutes/MT-2026-022.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-031</t>
+          <t>MT-2026-023</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>특이근태 예외 처리 방침 1차 협의</t>
+          <t>제6주차 정기 진척회의</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>의사결정</t>
+          <t>정기주간</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -7811,81 +7807,81 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>고객 인사팀 3인, 점포운영팀 2인, PM, 두루</t>
+          <t>전체 PL 5인, PMO</t>
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>4.3.2;4.6.3;5.1.4</t>
+          <t>3.1;3.2</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>DS-014;DS-015</t>
+          <t>DS-003</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>AI-072;AI-078</t>
+          <t>AI-045</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>D-01 근무 도메인 모델 확정 · D-02 편성 근거 3종 제공 의무화 · D-03 형평성 가중치 0.12→0.30 상향(최상위) · 예외 9종 처리 방침 확정</t>
+          <t>AS-IS 분석 결과 공유 · 현행 근무유형 47종 확인</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>특이근태 예외 23종 중 미결 14종 처리 방침 확정 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
+          <t>부문 표준 코드 매핑 기준 (결정필요일 2026-08-21 / 결정권자: 고객 점포운영팀)</t>
         </is>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-031.md</t>
+          <t>./minutes/MT-2026-023.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-032</t>
+          <t>MT-2026-024</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>제3차 운영위원회</t>
+          <t>요구사항 정의 중간 검토</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>운영위</t>
+          <t>고객협의</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>미르</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>운영위원 6인, PM, PMO</t>
+          <t>도담, 나루, 고객 인사팀 3인</t>
         </is>
       </c>
       <c r="G7" s="9" t="n">
@@ -7898,53 +7894,53 @@
         <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>4.2.3;5.2.3</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>DS-011</t>
+          <t>DS-005</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>AI-085</t>
+          <t>AI-048</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>CR-2026-007(휴게시간 자동분할) 승인 · 영향공수 +12MD</t>
+          <t>근무유형 표준 14종 요건 확정 · 가산 산정 원칙 합의</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
         <is>
-          <t>재기준선(안) 승인 (결정필요일 2026-10-08 / 결정권자: 운영위)</t>
+          <t>부문 표준 코드 매핑 기준 이월 (결정필요일 2026-08-21 / 결정권자: 고객 점포운영팀)</t>
         </is>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-032.md</t>
+          <t>./minutes/MT-2026-024.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-033</t>
+          <t>MT-2026-025</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>제12주차 정기 진척회의</t>
+          <t>제8주차 정기 진척회의</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -7963,137 +7959,141 @@
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>4.2.3;4.3.2;5.1.4</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr"/>
+          <t>3.2;3.3</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>DS-005;DS-008</t>
+        </is>
+      </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>AI-076</t>
+          <t>AI-051</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>결재선 매트릭스 초안 검토</t>
+          <t>기능 요구사항 정의서 검토 완료 · 부문 매핑 기준 확정</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>특이근태 예외 처리 방침 2회차 이월 (결정필요일 2026-10-01 / 결정권자: 고객 인사팀)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-033.md</t>
+          <t>./minutes/MT-2026-025.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-034</t>
+          <t>MT-2026-026</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>급여 연계 설계서 1차 검토</t>
+          <t>제9주차 정기 진척회의</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>설계리뷰</t>
+          <t>정기주간</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>너울</t>
+          <t>나루</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>너울, 도담, 고객 급여담당 2인</t>
+          <t>전체 PL 5인, PMO</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J9" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>4.5.2;6.2</t>
+          <t>4.1;4.2.1</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>DS-021</t>
+          <t>DS-009;DS-010</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>AI-076</t>
+          <t>AI-054</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>1차 반려 · 검토의견 23건(수당 산정 규칙 17건) 조치 후 재상정</t>
+          <t>아키텍처 정의서 초안 검토</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
         <is>
-          <t>단시간 초과근로 동의 절차 (결정필요일 2026-10-06 / 결정권자: 고객 인사팀)</t>
+          <t>편성 기준정보 수집 방식 (결정필요일 2026-09-11 / 결정권자: 고객 점포운영팀)</t>
         </is>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-034.md</t>
+          <t>./minutes/MT-2026-026.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-035</t>
+          <t>MT-2026-027</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>특이근태 예외 처리 방침 3차 협의</t>
+          <t>제10주차 정기 진척회의</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>의사결정</t>
+          <t>정기주간</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -8103,141 +8103,145 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>고객 인사팀 3인, 급여팀 1인, PM</t>
+          <t>전체 PL 5인, PMO</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>4.3.2;5.4.1;4.6.3</t>
+          <t>4.1;4.6.1</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>DS-014</t>
+          <t>DS-009;DS-016</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>AI-081</t>
+          <t>AI-057</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>확정 9종 기준 제약셋 우선 구현 · 미결 14종은 후처리 필터로 임시 우회 결정</t>
+          <t>공통 화면 표준 배포 · 기준정보 수집 템플릿 확정</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>하드 제약 충돌 5종(E-04/07/09/12/19) 방침 3회차 이월 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
+          <t>편성 기준정보 회신 기한 (결정필요일 2026-09-11 / 결정권자: 고객 점포운영팀)</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-035.md</t>
+          <t>./minutes/MT-2026-027.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-036</t>
+          <t>MT-2026-028</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>AI 스케줄 엔진 착수지연 이슈대응</t>
+          <t>설계 착수 리뷰</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>이슈해결</t>
+          <t>설계리뷰</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>벼리</t>
+          <t>두루</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>벼리, 나루, 미르, 새벽</t>
+          <t>두루, 여울, 너울, 새벽, 고객 인사팀 2인</t>
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>5.4.1;4.6.1</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr"/>
+          <t>4.2;4.3;4.6</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>DS-010;DS-013</t>
+        </is>
+      </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>AI-083</t>
+          <t>AI-061;AI-063</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>개발 2명 증원 품의 · 현업 의사결정 단일창구(인사팀 TF) 설치 · 기준 수립 워크숍 개최 합의</t>
+          <t>설계 표준·산출물 목록 확정 · 파일럿 3개점 선정</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>특이근태 예외 케이스 도출 범위 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>./minutes/MT-2026-036.md</t>
+          <t>./minutes/MT-2026-028.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-037</t>
+          <t>MT-2026-029</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>배정 최적화 1차 시뮬레이션 결과 리뷰</t>
+          <t>편성 기준정보 수집 현황 점검</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>설계리뷰</t>
+          <t>고객협의</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -8247,11 +8251,11 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>새벽, 두루, 모아, 고객 인사팀 1인</t>
+          <t>새벽, 너울, 고객 점포운영팀 3인</t>
         </is>
       </c>
       <c r="G12" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>2</v>
@@ -8260,34 +8264,618 @@
         <v>2</v>
       </c>
       <c r="J12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>4.6.1;4.6.2</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>DS-016</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>AI-069;AI-088</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>수집 템플릿 확정 · 대표 패턴만 입력 후 배수 규칙 자동 확장 합의</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>미회신 27개점 필요인원 기준 확정 (결정필요일 2026-09-29 / 결정권자: 고객 점포운영팀)</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-029.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-030</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>근로시간 준수 요건 확인 고객협의</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>고객협의</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>도담</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>도담, 나루, 고객 인사팀 2인</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>3.2.2</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>DS-006</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>AI-065</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>휴게시간 자동 분할 기록 원칙 확정</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>탄력근로제 단위기간 3개월/6개월 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀장)</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-030.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-031</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>특이근태 예외 처리 방침 1차 협의</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>의사결정</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>나루</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>고객 인사팀 3인, 점포운영팀 2인, PM, 두루</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="I14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>4.3.2;4.6.3;5.1.4</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>DS-014;DS-015</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>AI-072;AI-078</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>D-01 근무 도메인 모델 확정 · D-02 편성 근거 3종 제공 의무화 · D-03 형평성 가중치 0.12→0.30 상향(최상위) · 예외 9종 처리 방침 확정</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>특이근태 예외 23종 중 미결 14종 처리 방침 확정 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-031.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-032</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>제3차 운영위원회</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>운영위</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>미르</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>운영위원 6인, PM, PMO</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>4.2.3;5.2.3</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>DS-011</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>AI-085</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>CR-2026-007(휴게시간 자동분할) 승인 · 영향공수 +12MD</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>재기준선(안) 승인 (결정필요일 2026-10-08 / 결정권자: 운영위)</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-032.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-033</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>제12주차 정기 진척회의</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>정기주간</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>나루</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>전체 PL 5인, PMO</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>4.2.3;4.3.2;5.1.4</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>AI-076</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>결재선 매트릭스 초안 검토</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>특이근태 예외 처리 방침 2회차 이월 (결정필요일 2026-10-01 / 결정권자: 고객 인사팀)</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-033.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-034</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>급여 연계 설계서 1차 검토</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>설계리뷰</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>너울</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>너울, 도담, 고객 급여담당 2인</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>4.5.2;6.2</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>DS-021</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>AI-076</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>1차 반려 · 검토의견 23건(수당 산정 규칙 17건) 조치 후 재상정</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>단시간 초과근로 동의 절차 (결정필요일 2026-10-06 / 결정권자: 고객 인사팀)</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-034.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-035</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>특이근태 예외 처리 방침 3차 협의</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>의사결정</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>나루</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>고객 인사팀 3인, 급여팀 1인, PM</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>4.3.2;5.4.1;4.6.3</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>DS-014</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>AI-081</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>확정 9종 기준 제약셋 우선 구현 · 미결 14종은 후처리 필터로 임시 우회 결정</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>하드 제약 충돌 5종(E-04/07/09/12/19) 방침 3회차 이월 (결정필요일 2026-09-18 / 결정권자: 고객 인사팀)</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-035.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-036</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>AI 스케줄 엔진 착수지연 이슈대응</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>이슈해결</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>벼리</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>벼리, 나루, 미르, 새벽</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>5.4.1;4.6.1</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr"/>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>AI-083</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>개발 2명 증원 품의 · 현업 의사결정 단일창구(인사팀 TF) 설치 · 기준 수립 워크숍 개최 합의</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>./minutes/MT-2026-036.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-037</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>배정 최적화 1차 시뮬레이션 결과 리뷰</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>설계리뷰</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>새벽, 두루, 모아, 고객 인사팀 1인</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>4.6.2;6.3</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>DS-015;DS-016</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>AI-090</t>
         </is>
       </c>
-      <c r="N12" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>미달 판정 · 형평성 상한을 하드 제약(HC-13)으로 승격 의결 · 입력 조건 해소 후 2차 시뮬레이션</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O20" s="9" t="inlineStr">
         <is>
           <t>형평성 누적 대상 기간 3/6/12개월 (결정필요일 2026-10-16 / 결정권자: 고객 인사팀)</t>
         </is>
       </c>
-      <c r="P12" s="9" t="inlineStr">
+      <c r="P20" s="9" t="inlineStr">
         <is>
           <t>./minutes/MT-2026-037.md</t>
         </is>
@@ -8307,7 +8895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8487,22 +9075,22 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>AI-065</t>
+          <t>AI-041</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-030</t>
+          <t>MT-2026-022</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>탄력근로제 단위기간 확정 요청 공문 발송 및 회신 수령</t>
+          <t>AS-IS 실태조사 대상 점포 목록 확정 및 조사표 배포</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>대외협의</t>
+          <t>산출물보완</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -8512,134 +9100,142 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr"/>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>DS-006</t>
+          <t>DS-003</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O4" s="9" t="inlineStr">
         <is>
-          <t>2차 독촉 10-01. 잠정 3개월 기준 설계 병행</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>AI-069</t>
+          <t>AI-045</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-029</t>
+          <t>MT-2026-023</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>미회신 27개점 필요인원 기준 회신 확보</t>
+          <t>현행 근무유형 47종 조사 결과 정리</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>대외협의</t>
+          <t>기술검토</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>새벽</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr"/>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>4.6.1</t>
+          <t>3.1;4.3.2</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>DS-016</t>
+          <t>DS-003</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O5" s="9" t="inlineStr">
         <is>
-          <t>16개점은 기준 자체가 부재 — 본사 초안 작성 방식으로 전환</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>AI-072</t>
+          <t>AI-048</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-031</t>
+          <t>MT-2026-024</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>점포 유형별(마트/백화점/트레이더스) 근태 승인 결재선 매트릭스 확정</t>
+          <t>근무유형 표준 14종 요건 확정본 작성</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -8649,36 +9245,40 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>여울</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>5.1.4</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>DS-010</t>
+          <t>DS-005</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -8688,29 +9288,29 @@
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>담당 재지정(여울 → 두루) 검토 중</t>
+          <t>완료 · DS-014 입력값</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>AI-076</t>
+          <t>AI-051</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-034</t>
+          <t>MT-2026-025</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>급여 연계 설계서 검토의견 23건 조치 및 재상정</t>
+          <t>부문 표준 코드 매핑표 작성</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -8725,31 +9325,35 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>4.5.2</t>
+          <t>3.2;4.5.1</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>DS-021</t>
+          <t>DS-008</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -8764,29 +9368,29 @@
       </c>
       <c r="O7" s="9" t="inlineStr">
         <is>
-          <t>14건 조치완료 / 9건 미조치(4건은 선행 산출물 미확정 종속)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>AI-078</t>
+          <t>AI-054</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-031</t>
+          <t>MT-2026-026</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>특이근태 예외 케이스 전수 도출 및 처리 방침(안) 작성</t>
+          <t>아키텍처 정의서 검토의견 6건 조치</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>기술검토</t>
+          <t>산출물보완</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -8796,17 +9400,17 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -8819,17 +9423,17 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>DS-014</t>
+          <t>DS-009</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -8839,50 +9443,54 @@
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>23종 도출 완료(2일 초과). 9종 확정 / 14종 인사팀 회신 대기</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>AI-081</t>
+          <t>AI-057</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-035</t>
+          <t>MT-2026-027</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>확정 9종 기준 제약셋 정의 및 최적화 엔진 병행개발 착수</t>
+          <t>편성 기준정보 수집 템플릿 배포(71개점)</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>리스크대응</t>
+          <t>대외협의</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>벼리</t>
+          <t>새벽</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr"/>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>진행</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
@@ -8890,12 +9498,12 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>4.6.1</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>DS-015</t>
+          <t>DS-016</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -8910,44 +9518,44 @@
       </c>
       <c r="O9" s="9" t="inlineStr">
         <is>
-          <t>Mock 제약셋 작성 중</t>
+          <t>완료 · 회신 대기 시작</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>AI-083</t>
+          <t>AI-065</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-036</t>
+          <t>MT-2026-030</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>개발인력 2명 증원 투입 품의 및 승인</t>
+          <t>탄력근로제 단위기간 확정 요청 공문 발송 및 회신 수령</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>자원조치</t>
+          <t>대외협의</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>나루</t>
+          <t>도담</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr"/>
@@ -8957,14 +9565,18 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>5.4.1;5.1.4</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr"/>
+          <t>3.2.2</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>DS-006</t>
+        </is>
+      </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
           <t>H</t>
@@ -8972,49 +9584,49 @@
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>9월 1일자 투입 목표</t>
+          <t>2차 독촉 10-01. 잠정 3개월 기준 설계 병행</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>AI-085</t>
+          <t>AI-069</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-032</t>
+          <t>MT-2026-029</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>CR-2026-007 반영 재기준선(안) 작성</t>
+          <t>미회신 27개점 필요인원 기준 회신 확보</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>결정이행</t>
+          <t>대외협의</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>미르</t>
+          <t>새벽</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr"/>
@@ -9024,64 +9636,68 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>4.2.3;5.2.3</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr"/>
+          <t>4.6.1</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>DS-016</t>
+        </is>
+      </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>10-12 운영위 상정 예정</t>
+          <t>16개점은 기준 자체가 부재 — 본사 초안 작성 방식으로 전환</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>AI-088</t>
+          <t>AI-072</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-029</t>
+          <t>MT-2026-031</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>기준 수립 워크숍 개최(권역별 4회) 및 초안 배포</t>
+          <t>점포 유형별(마트/백화점/트레이더스) 근태 승인 결재선 매트릭스 확정</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>대외협의</t>
+          <t>결정이행</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>새벽</t>
+          <t>여울</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr"/>
@@ -9091,16 +9707,16 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>4.6.1</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>DS-016</t>
+          <t>DS-010</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -9110,49 +9726,49 @@
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>기준 부재 16개점 대상. 10-13 워크숍 착수</t>
+          <t>담당 재지정(여울 → 두루) 검토 중</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>AI-090</t>
+          <t>AI-076</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-037</t>
+          <t>MT-2026-034</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>형평성 상한(HC-13) 하드 제약 승격 설계 및 재검증</t>
+          <t>급여 연계 설계서 검토의견 23건 조치 및 재상정</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>기술검토</t>
+          <t>산출물보완</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>새벽</t>
+          <t>너울</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr"/>
@@ -9162,16 +9778,16 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>4.6.2</t>
+          <t>4.5.2</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>DS-015</t>
+          <t>DS-021</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
@@ -9186,49 +9802,49 @@
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>지니계수 0.31 → 0.15 이하 개선 목적</t>
+          <t>14건 조치완료 / 9건 미조치(4건은 선행 산출물 미확정 종속)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>AI-061</t>
+          <t>AI-078</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>MT-2026-028</t>
+          <t>MT-2026-031</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>공통 화면 표준 가이드 배포</t>
+          <t>특이근태 예외 케이스 전수 도출 및 처리 방침(안) 작성</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>산출물보완</t>
+          <t>기술검토</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>여울</t>
+          <t>두루</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -9241,17 +9857,17 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>DS-010</t>
+          <t>DS-014</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -9261,76 +9877,498 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>23종 도출 완료(2일 초과). 9종 확정 / 14종 인사팀 회신 대기</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
+          <t>AI-081</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-035</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>확정 9종 기준 제약셋 정의 및 최적화 엔진 병행개발 착수</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>리스크대응</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>벼리</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>5.4.1</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>DS-015</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>Mock 제약셋 작성 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>AI-083</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-036</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>개발인력 2명 증원 투입 품의 및 승인</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>자원조치</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>나루</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>5.4.1;5.1.4</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>9월 1일자 투입 목표</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>AI-085</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-032</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>CR-2026-007 반영 재기준선(안) 작성</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>결정이행</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>미르</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>4.2.3;5.2.3</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>10-12 운영위 상정 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>AI-088</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-029</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>기준 수립 워크숍 개최(권역별 4회) 및 초안 배포</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>대외협의</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>4.6.1</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>DS-016</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>기준 부재 16개점 대상. 10-13 워크숍 착수</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>AI-090</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-037</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>형평성 상한(HC-13) 하드 제약 승격 설계 및 재검증</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>기술검토</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>새벽</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>4.6.2</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>DS-015</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>지니계수 0.31 → 0.15 이하 개선 목적</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>AI-061</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>MT-2026-028</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>공통 화면 표준 가이드 배포</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>산출물보완</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>여울</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>DS-010</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
           <t>AI-063</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>MT-2026-028</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>파일럿 3개점 근태단말 테스트 계정 발급 요청</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>대외협의</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>바름</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="J15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -11210,7 +12248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11699,29 +12737,26 @@
         <v>7</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>4900</v>
-      </c>
-      <c r="J8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>심의대기</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>4.6.4;5.4.3</t>
+        </is>
+      </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>4.6.4;5.4.3</t>
-        </is>
-      </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P8" s="9" t="inlineStr"/>
+      <c r="O8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -11763,33 +12798,30 @@
         <v>34</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>23800</v>
-      </c>
-      <c r="J9" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
           <t>반려</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr"/>
+      <c r="O9" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/PMO_산출물_표준양식_v1.2.xlsx
+++ b/templates/PMO_산출물_표준양식_v1.2.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>점포 근태·AI 스케줄 관리 시스템 구축 (계약금액 500,000천원 / 2026-07-01 ~ 2026-12-31)</t>
+          <t>자동 스케줄 관리 시스템 구축 (계약금액 500,000천원 / 2026-07-01 ~ 2026-12-31)</t>
         </is>
       </c>
     </row>
